--- a/data/spreadsheet/Payroll Spreadsheet.xlsx
+++ b/data/spreadsheet/Payroll Spreadsheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Insulpro\system\spreadsheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Kenny-pc\d\Insulpro\data\spreadsheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{693B007C-E604-4EAB-AD78-D0AE77881D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071F0F4D-2490-4E8E-9A35-FCAEEE802451}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="841" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="841" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Payroll Summary" sheetId="39" r:id="rId1"/>
@@ -846,22 +846,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE9C6EB5-6956-4042-997B-9C05D75A32D2}">
   <dimension ref="A1:E30"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="28.7265625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="15.7265625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="11" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" style="11" customWidth="1"/>
-    <col min="6" max="16384" width="8.81640625" style="11"/>
+    <col min="1" max="1" width="28.77734375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" style="11" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="11" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" style="11" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" style="11" customWidth="1"/>
+    <col min="6" max="16384" width="8.77734375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" s="28" t="s">
         <v>31</v>
       </c>
@@ -878,7 +878,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" s="29">
         <f>'Emp1&amp;Emp2'!B1</f>
         <v>0</v>
@@ -897,7 +897,7 @@
       </c>
       <c r="E4" s="35"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" s="29">
         <f>'Emp1&amp;Emp2'!B19</f>
         <v>0</v>
@@ -916,7 +916,7 @@
       </c>
       <c r="E5" s="36"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" s="29">
         <f>'Emp3&amp;Emp4'!B1</f>
         <v>0</v>
@@ -935,7 +935,7 @@
       </c>
       <c r="E6" s="35"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" s="29">
         <f>'Emp3&amp;Emp4'!B19</f>
         <v>0</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="E7" s="35"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" s="29">
         <f>'Emp5&amp;Emp6'!B1</f>
         <v>0</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="E8" s="35"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" s="29">
         <f>'Emp5&amp;Emp6'!B19</f>
         <v>0</v>
@@ -992,7 +992,7 @@
       </c>
       <c r="E9" s="35"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" s="29">
         <f>'Emp7&amp;Emp8'!B1</f>
         <v>0</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E10" s="35"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" s="29">
         <f>'Emp7&amp;Emp8'!B19</f>
         <v>0</v>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="E11" s="35"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="29">
         <f>'Emp9&amp;Emp10'!B1</f>
         <v>0</v>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="E12" s="35"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" s="29">
         <f>'Emp9&amp;Emp10'!B19</f>
         <v>0</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="E13" s="35"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" s="29">
         <f>'Emp11&amp;Emp12'!B1</f>
         <v>0</v>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E14" s="35"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" s="29">
         <f>'Emp11&amp;Emp12'!B19</f>
         <v>0</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="E15" s="35"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" s="29">
         <f>'Emp13&amp;Emp14'!B1</f>
         <v>0</v>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="E16" s="35"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" s="29">
         <f>'Emp13&amp;Emp14'!B19</f>
         <v>0</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E17" s="35"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18" s="29">
         <f>'Emp15&amp;Open'!B1</f>
         <v>0</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E18" s="35"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21" s="28" t="s">
         <v>35</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22" s="12" t="s">
         <v>38</v>
       </c>
@@ -1191,46 +1191,46 @@
       <c r="D22" s="31"/>
       <c r="E22" s="31"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A23" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B23" s="31">
-        <v>923.08</v>
+        <v>1057.7</v>
       </c>
       <c r="C23" s="31"/>
       <c r="D23" s="31"/>
       <c r="E23" s="31"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A24" s="12"/>
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
       <c r="D24" s="31"/>
       <c r="E24" s="31"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A25" s="12"/>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
       <c r="E25" s="31"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A27" s="16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A28" s="12" t="s">
         <v>43</v>
       </c>
       <c r="B28" s="32">
         <f>SUM(B22:E25)</f>
-        <v>2078.08</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+        <v>2212.6999999999998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A29" s="12" t="s">
         <v>44</v>
       </c>
@@ -1239,13 +1239,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A30" s="12" t="s">
         <v>40</v>
       </c>
       <c r="B30" s="32">
         <f>SUM(B28:B29)</f>
-        <v>2078.08</v>
+        <v>2212.6999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -1263,21 +1263,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.81640625" customWidth="1"/>
-    <col min="2" max="2" width="13.1796875" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" customWidth="1"/>
-    <col min="6" max="6" width="11.26953125" customWidth="1"/>
-    <col min="7" max="7" width="10.453125" customWidth="1"/>
-    <col min="8" max="8" width="11.453125" customWidth="1"/>
-    <col min="9" max="9" width="10.453125" customWidth="1"/>
-    <col min="17" max="17" width="11.81640625" customWidth="1"/>
-    <col min="27" max="27" width="10.54296875" customWidth="1"/>
+    <col min="1" max="1" width="25.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="10.44140625" customWidth="1"/>
+    <col min="17" max="17" width="11.77734375" customWidth="1"/>
+    <col min="27" max="27" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1307,7 +1307,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="20.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="20.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -1394,7 +1394,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -1511,7 +1511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1541,7 +1541,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -1577,7 +1577,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="19.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -1678,9 +1678,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1710,7 +1710,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -1797,7 +1797,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1944,7 +1944,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -1980,7 +1980,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -2081,9 +2081,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2113,7 +2113,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -2200,7 +2200,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -2347,7 +2347,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -2383,7 +2383,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -2481,9 +2481,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28E20304-5F04-44BA-8589-C60E0AB00EA2}">
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2513,7 +2513,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -2600,7 +2600,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -2747,7 +2747,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -2783,7 +2783,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -2881,9 +2881,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A677CCE-55D1-4BB3-A65B-3285358DF79C}">
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2913,7 +2913,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -3000,7 +3000,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -3147,7 +3147,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -3183,7 +3183,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -3281,9 +3281,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A5F13E-5A6D-4F38-A14E-D14DF60A7870}">
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3313,7 +3313,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -3400,7 +3400,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -3547,7 +3547,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -3583,7 +3583,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -3681,9 +3681,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C843986-6681-4E2B-8761-DCA4DDD60505}">
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3713,7 +3713,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -3800,7 +3800,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -3947,7 +3947,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -3983,7 +3983,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -4081,9 +4081,9 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1A0ACC-16C7-437F-A7D0-423284689E08}">
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4113,7 +4113,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -4200,7 +4200,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -4347,7 +4347,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -4383,7 +4383,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -4481,9 +4481,9 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{754B6EEA-37FB-4D5C-86AC-DB03916EA851}">
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4513,7 +4513,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -4600,7 +4600,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -4747,7 +4747,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -4783,7 +4783,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -4881,9 +4881,9 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EF0EFA6-059F-498B-A9BF-121B0376F9B5}">
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4913,7 +4913,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -5000,7 +5000,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -5147,7 +5147,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -5183,7 +5183,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -5284,29 +5284,29 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" style="11" customWidth="1"/>
-    <col min="2" max="2" width="12.26953125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="8.81640625" style="11"/>
-    <col min="4" max="4" width="12.1796875" style="11" customWidth="1"/>
-    <col min="5" max="5" width="9.1796875" style="11" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" style="11"/>
-    <col min="7" max="7" width="10.54296875" style="11" customWidth="1"/>
-    <col min="8" max="8" width="8.81640625" style="11" customWidth="1"/>
-    <col min="9" max="9" width="8.81640625" style="11"/>
-    <col min="10" max="10" width="11.7265625" style="11" customWidth="1"/>
-    <col min="11" max="12" width="10.1796875" style="11" customWidth="1"/>
-    <col min="13" max="13" width="10.453125" style="11" customWidth="1"/>
-    <col min="14" max="16384" width="8.81640625" style="11"/>
+    <col min="1" max="1" width="9.77734375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="8.77734375" style="11"/>
+    <col min="4" max="4" width="12.21875" style="11" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" style="11" customWidth="1"/>
+    <col min="6" max="6" width="8.77734375" style="11"/>
+    <col min="7" max="7" width="10.5546875" style="11" customWidth="1"/>
+    <col min="8" max="8" width="8.77734375" style="11" customWidth="1"/>
+    <col min="9" max="9" width="8.77734375" style="11"/>
+    <col min="10" max="10" width="11.77734375" style="11" customWidth="1"/>
+    <col min="11" max="12" width="10.21875" style="11" customWidth="1"/>
+    <col min="13" max="13" width="10.44140625" style="11" customWidth="1"/>
+    <col min="14" max="16384" width="8.77734375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="17.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="17.55" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" s="12">
         <f>Emp1Record!B3</f>
         <v>0</v>
@@ -5401,7 +5401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
       <c r="B5" s="14"/>
       <c r="C5" s="12">
@@ -5434,7 +5434,7 @@
       <c r="L5" s="30"/>
       <c r="M5" s="14"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="C6" s="14"/>
@@ -5461,7 +5461,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -5482,7 +5482,7 @@
       <c r="L7" s="30"/>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -5503,7 +5503,7 @@
       <c r="L8" s="30"/>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -5521,7 +5521,7 @@
       <c r="L9" s="30"/>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -5542,7 +5542,7 @@
       <c r="L10" s="30"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -5560,7 +5560,7 @@
       <c r="L11" s="30"/>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -5578,7 +5578,7 @@
       <c r="L12" s="30"/>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -5596,7 +5596,7 @@
       <c r="L13" s="30"/>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" s="15"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -5614,7 +5614,7 @@
       <c r="L14" s="30"/>
       <c r="M14" s="17"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" s="23">
         <f>A4*'Pay Rates'!B3</f>
         <v>0</v>
@@ -5668,7 +5668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
         <v>30</v>
       </c>
@@ -5688,12 +5688,12 @@
       <c r="L16" s="20"/>
       <c r="M16" s="21"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
         <v>1</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" s="12">
         <f>Emp2Record!B3</f>
         <v>0</v>
@@ -5788,7 +5788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="12">
@@ -5821,7 +5821,7 @@
       <c r="L23" s="30"/>
       <c r="M23" s="14"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="14"/>
@@ -5848,7 +5848,7 @@
       <c r="L24" s="30"/>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -5869,7 +5869,7 @@
       <c r="L25" s="30"/>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -5890,7 +5890,7 @@
       <c r="L26" s="30"/>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" s="15"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -5908,7 +5908,7 @@
       <c r="L27" s="30"/>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -5929,7 +5929,7 @@
       <c r="L28" s="30"/>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" s="15"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -5947,7 +5947,7 @@
       <c r="L29" s="30"/>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" s="15"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -5965,7 +5965,7 @@
       <c r="L30" s="30"/>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -5983,7 +5983,7 @@
       <c r="L31" s="30"/>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" s="15"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -6001,7 +6001,7 @@
       <c r="L32" s="30"/>
       <c r="M32" s="17"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" s="23">
         <f>A22*'Pay Rates'!B3</f>
         <v>0</v>
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
         <v>30</v>
       </c>
@@ -6087,9 +6087,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{703B3B20-CC88-424C-A39E-4B0BEB4393EE}">
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6119,7 +6119,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -6206,7 +6206,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -6353,7 +6353,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -6389,7 +6389,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -6487,9 +6487,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27AD96D0-AD57-4AF3-BDFD-E23A4D35E9D6}">
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6519,7 +6519,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -6606,7 +6606,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -6753,7 +6753,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -6789,7 +6789,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -6887,9 +6887,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926B46EA-0502-4501-A495-F8D82C1430FE}">
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6919,7 +6919,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -7006,7 +7006,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -7123,7 +7123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -7153,7 +7153,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -7189,7 +7189,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -7287,9 +7287,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0F24925-CC7E-4645-8B37-C6CEE61A9CF7}">
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7319,7 +7319,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -7406,7 +7406,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -7553,7 +7553,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -7589,7 +7589,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -7687,9 +7687,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B00725-CF68-4795-BE3E-4C5A0B246D48}">
   <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7719,7 +7719,7 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -7806,7 +7806,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -7953,7 +7953,7 @@
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
     </row>
-    <row r="5" spans="1:29" ht="16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" ht="15" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="8" t="s">
         <v>22</v>
@@ -7989,7 +7989,7 @@
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
     </row>
-    <row r="6" spans="1:29" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" ht="30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
@@ -8087,19 +8087,19 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B23A72FF-0135-496D-8203-1C66C48918D4}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="21.1796875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" style="11" customWidth="1"/>
-    <col min="3" max="16384" width="8.81640625" style="11"/>
+    <col min="1" max="1" width="21.21875" style="11" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" style="11" customWidth="1"/>
+    <col min="3" max="16384" width="8.77734375" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" s="24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="25" t="s">
         <v>34</v>
       </c>
@@ -8107,79 +8107,79 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="26"/>
       <c r="B3" s="27"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="26"/>
       <c r="B5" s="27"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="26"/>
       <c r="B6" s="27"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="26"/>
       <c r="B7" s="27"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="26"/>
       <c r="B8" s="27"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="26"/>
       <c r="B9" s="27"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" s="26"/>
       <c r="B10" s="27"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="26"/>
       <c r="B11" s="27"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="26"/>
       <c r="B12" s="27"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" s="26"/>
       <c r="B13" s="27"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" s="26"/>
       <c r="B14" s="27"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" s="26"/>
       <c r="B15" s="27"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" s="26"/>
       <c r="B16" s="27"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" s="26"/>
       <c r="B17" s="27"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" s="26"/>
       <c r="B18" s="27"/>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" s="26"/>
       <c r="B19" s="27"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" s="26"/>
       <c r="B20" s="27"/>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" s="26"/>
       <c r="B21" s="27"/>
     </row>
@@ -8195,17 +8195,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="10.54296875" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="9.7265625" customWidth="1"/>
-    <col min="9" max="9" width="10.26953125" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" customWidth="1"/>
+    <col min="9" max="9" width="10.21875" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>25</v>
       </c>
@@ -8222,7 +8222,7 @@
       <c r="L1" s="11"/>
       <c r="M1" s="11"/>
     </row>
-    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -8237,7 +8237,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="1:13" ht="16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -8278,7 +8278,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A4" s="12">
         <f>Emp3Record!B3</f>
         <v>0</v>
@@ -8332,7 +8332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
       <c r="B5" s="14"/>
       <c r="C5" s="12">
@@ -8365,7 +8365,7 @@
       <c r="L5" s="30"/>
       <c r="M5" s="14"/>
     </row>
-    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="C6" s="14"/>
@@ -8392,7 +8392,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -8413,7 +8413,7 @@
       <c r="L7" s="30"/>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -8434,7 +8434,7 @@
       <c r="L8" s="30"/>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -8452,7 +8452,7 @@
       <c r="L9" s="30"/>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -8473,7 +8473,7 @@
       <c r="L10" s="30"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -8491,7 +8491,7 @@
       <c r="L11" s="30"/>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -8509,7 +8509,7 @@
       <c r="L12" s="30"/>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -8527,7 +8527,7 @@
       <c r="L13" s="30"/>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A14" s="15"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -8545,7 +8545,7 @@
       <c r="L14" s="30"/>
       <c r="M14" s="17"/>
     </row>
-    <row r="15" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A15" s="23">
         <f>A4*'Pay Rates'!B3</f>
         <v>0</v>
@@ -8599,7 +8599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
         <v>30</v>
       </c>
@@ -8619,7 +8619,7 @@
       <c r="L16" s="20"/>
       <c r="M16" s="21"/>
     </row>
-    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -8634,7 +8634,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -8649,7 +8649,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
     </row>
-    <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -8666,7 +8666,7 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
     </row>
-    <row r="20" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -8681,7 +8681,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:13" ht="16" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>1</v>
       </c>
@@ -8722,7 +8722,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A22" s="12">
         <f>Emp4Record!B3</f>
         <v>0</v>
@@ -8776,7 +8776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="12">
@@ -8809,7 +8809,7 @@
       <c r="L23" s="30"/>
       <c r="M23" s="14"/>
     </row>
-    <row r="24" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="14"/>
@@ -8836,7 +8836,7 @@
       <c r="L24" s="30"/>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -8857,7 +8857,7 @@
       <c r="L25" s="30"/>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -8878,7 +8878,7 @@
       <c r="L26" s="30"/>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A27" s="15"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -8896,7 +8896,7 @@
       <c r="L27" s="30"/>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -8917,7 +8917,7 @@
       <c r="L28" s="30"/>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A29" s="15"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -8935,7 +8935,7 @@
       <c r="L29" s="30"/>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A30" s="15"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -8953,7 +8953,7 @@
       <c r="L30" s="30"/>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -8971,7 +8971,7 @@
       <c r="L31" s="30"/>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A32" s="15"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -8989,7 +8989,7 @@
       <c r="L32" s="30"/>
       <c r="M32" s="17"/>
     </row>
-    <row r="33" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A33" s="23">
         <f>A22*'Pay Rates'!B3</f>
         <v>0</v>
@@ -9043,7 +9043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
         <v>30</v>
       </c>
@@ -9078,9 +9078,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>25</v>
       </c>
@@ -9097,7 +9097,7 @@
       <c r="L1" s="11"/>
       <c r="M1" s="11"/>
     </row>
-    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -9112,7 +9112,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A4" s="12">
         <f>Emp5Record!B3</f>
         <v>0</v>
@@ -9207,7 +9207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
       <c r="B5" s="14"/>
       <c r="C5" s="12">
@@ -9240,7 +9240,7 @@
       <c r="L5" s="30"/>
       <c r="M5" s="14"/>
     </row>
-    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="C6" s="14"/>
@@ -9267,7 +9267,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -9288,7 +9288,7 @@
       <c r="L7" s="30"/>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -9309,7 +9309,7 @@
       <c r="L8" s="30"/>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -9327,7 +9327,7 @@
       <c r="L9" s="30"/>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -9348,7 +9348,7 @@
       <c r="L10" s="30"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -9366,7 +9366,7 @@
       <c r="L11" s="30"/>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -9384,7 +9384,7 @@
       <c r="L12" s="30"/>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -9402,7 +9402,7 @@
       <c r="L13" s="30"/>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A14" s="15"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -9420,7 +9420,7 @@
       <c r="L14" s="30"/>
       <c r="M14" s="17"/>
     </row>
-    <row r="15" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A15" s="23">
         <f>A4*'Pay Rates'!B3</f>
         <v>0</v>
@@ -9474,7 +9474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
         <v>30</v>
       </c>
@@ -9494,7 +9494,7 @@
       <c r="L16" s="20"/>
       <c r="M16" s="21"/>
     </row>
-    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -9509,7 +9509,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -9524,7 +9524,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
     </row>
-    <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -9541,7 +9541,7 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
     </row>
-    <row r="20" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -9556,7 +9556,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:13" ht="32" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>1</v>
       </c>
@@ -9597,7 +9597,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A22" s="12">
         <f>Emp6Record!B3</f>
         <v>0</v>
@@ -9651,7 +9651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="12">
@@ -9684,7 +9684,7 @@
       <c r="L23" s="30"/>
       <c r="M23" s="14"/>
     </row>
-    <row r="24" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="14"/>
@@ -9711,7 +9711,7 @@
       <c r="L24" s="30"/>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -9732,7 +9732,7 @@
       <c r="L25" s="30"/>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -9753,7 +9753,7 @@
       <c r="L26" s="30"/>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A27" s="15"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -9771,7 +9771,7 @@
       <c r="L27" s="30"/>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -9792,7 +9792,7 @@
       <c r="L28" s="30"/>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A29" s="15"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -9810,7 +9810,7 @@
       <c r="L29" s="30"/>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A30" s="15"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -9828,7 +9828,7 @@
       <c r="L30" s="30"/>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -9846,7 +9846,7 @@
       <c r="L31" s="30"/>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A32" s="15"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -9864,7 +9864,7 @@
       <c r="L32" s="30"/>
       <c r="M32" s="17"/>
     </row>
-    <row r="33" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A33" s="23">
         <f>A22*'Pay Rates'!B3</f>
         <v>0</v>
@@ -9918,7 +9918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
         <v>30</v>
       </c>
@@ -9953,9 +9953,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>25</v>
       </c>
@@ -9972,7 +9972,7 @@
       <c r="L1" s="11"/>
       <c r="M1" s="11"/>
     </row>
-    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -9987,7 +9987,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -10028,7 +10028,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A4" s="12">
         <f>Emp7Record!B3</f>
         <v>0</v>
@@ -10082,7 +10082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
       <c r="B5" s="14"/>
       <c r="C5" s="12">
@@ -10115,7 +10115,7 @@
       <c r="L5" s="30"/>
       <c r="M5" s="14"/>
     </row>
-    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="C6" s="14"/>
@@ -10142,7 +10142,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -10163,7 +10163,7 @@
       <c r="L7" s="30"/>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -10184,7 +10184,7 @@
       <c r="L8" s="30"/>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -10202,7 +10202,7 @@
       <c r="L9" s="30"/>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -10223,7 +10223,7 @@
       <c r="L10" s="30"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -10241,7 +10241,7 @@
       <c r="L11" s="30"/>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -10259,7 +10259,7 @@
       <c r="L12" s="30"/>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -10277,7 +10277,7 @@
       <c r="L13" s="30"/>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A14" s="15"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -10295,7 +10295,7 @@
       <c r="L14" s="30"/>
       <c r="M14" s="17"/>
     </row>
-    <row r="15" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A15" s="23">
         <f>A4*'Pay Rates'!B3</f>
         <v>0</v>
@@ -10349,7 +10349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
         <v>30</v>
       </c>
@@ -10369,7 +10369,7 @@
       <c r="L16" s="20"/>
       <c r="M16" s="21"/>
     </row>
-    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -10384,7 +10384,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -10399,7 +10399,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
     </row>
-    <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -10416,7 +10416,7 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
     </row>
-    <row r="20" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -10431,7 +10431,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:13" ht="32" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>1</v>
       </c>
@@ -10472,7 +10472,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A22" s="12">
         <f>Emp8Record!B3</f>
         <v>0</v>
@@ -10526,7 +10526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="12">
@@ -10559,7 +10559,7 @@
       <c r="L23" s="30"/>
       <c r="M23" s="14"/>
     </row>
-    <row r="24" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="14"/>
@@ -10586,7 +10586,7 @@
       <c r="L24" s="30"/>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -10607,7 +10607,7 @@
       <c r="L25" s="30"/>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -10628,7 +10628,7 @@
       <c r="L26" s="30"/>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A27" s="15"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -10646,7 +10646,7 @@
       <c r="L27" s="30"/>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -10667,7 +10667,7 @@
       <c r="L28" s="30"/>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A29" s="15"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -10685,7 +10685,7 @@
       <c r="L29" s="30"/>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A30" s="15"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -10703,7 +10703,7 @@
       <c r="L30" s="30"/>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -10721,7 +10721,7 @@
       <c r="L31" s="30"/>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A32" s="15"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -10739,7 +10739,7 @@
       <c r="L32" s="30"/>
       <c r="M32" s="17"/>
     </row>
-    <row r="33" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A33" s="23">
         <f>A22*'Pay Rates'!B3</f>
         <v>0</v>
@@ -10793,7 +10793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
         <v>30</v>
       </c>
@@ -10828,9 +10828,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>25</v>
       </c>
@@ -10847,7 +10847,7 @@
       <c r="L1" s="11"/>
       <c r="M1" s="11"/>
     </row>
-    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -10862,7 +10862,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -10903,7 +10903,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A4" s="12">
         <f>Emp9Record!B3</f>
         <v>0</v>
@@ -10957,7 +10957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
       <c r="B5" s="14"/>
       <c r="C5" s="12">
@@ -10990,7 +10990,7 @@
       <c r="L5" s="30"/>
       <c r="M5" s="14"/>
     </row>
-    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="C6" s="14"/>
@@ -11017,7 +11017,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -11038,7 +11038,7 @@
       <c r="L7" s="30"/>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -11059,7 +11059,7 @@
       <c r="L8" s="30"/>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -11077,7 +11077,7 @@
       <c r="L9" s="30"/>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -11098,7 +11098,7 @@
       <c r="L10" s="30"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -11116,7 +11116,7 @@
       <c r="L11" s="30"/>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -11134,7 +11134,7 @@
       <c r="L12" s="30"/>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -11152,7 +11152,7 @@
       <c r="L13" s="30"/>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A14" s="15"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -11170,7 +11170,7 @@
       <c r="L14" s="30"/>
       <c r="M14" s="17"/>
     </row>
-    <row r="15" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A15" s="23">
         <f>A4*'Pay Rates'!B3</f>
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
         <v>30</v>
       </c>
@@ -11244,7 +11244,7 @@
       <c r="L16" s="20"/>
       <c r="M16" s="21"/>
     </row>
-    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -11259,7 +11259,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -11274,7 +11274,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
     </row>
-    <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -11291,7 +11291,7 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
     </row>
-    <row r="20" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -11306,7 +11306,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:13" ht="32" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>1</v>
       </c>
@@ -11347,7 +11347,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A22" s="12">
         <f>Emp10Record!B3</f>
         <v>0</v>
@@ -11401,7 +11401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="12">
@@ -11434,7 +11434,7 @@
       <c r="L23" s="30"/>
       <c r="M23" s="14"/>
     </row>
-    <row r="24" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="14"/>
@@ -11461,7 +11461,7 @@
       <c r="L24" s="30"/>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -11482,7 +11482,7 @@
       <c r="L25" s="30"/>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -11503,7 +11503,7 @@
       <c r="L26" s="30"/>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A27" s="15"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -11521,7 +11521,7 @@
       <c r="L27" s="30"/>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -11542,7 +11542,7 @@
       <c r="L28" s="30"/>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A29" s="15"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -11560,7 +11560,7 @@
       <c r="L29" s="30"/>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A30" s="15"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -11578,7 +11578,7 @@
       <c r="L30" s="30"/>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -11596,7 +11596,7 @@
       <c r="L31" s="30"/>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A32" s="15"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -11614,7 +11614,7 @@
       <c r="L32" s="30"/>
       <c r="M32" s="17"/>
     </row>
-    <row r="33" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A33" s="23">
         <f>A22*'Pay Rates'!B3</f>
         <v>0</v>
@@ -11668,7 +11668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
         <v>30</v>
       </c>
@@ -11703,9 +11703,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>25</v>
       </c>
@@ -11722,7 +11722,7 @@
       <c r="L1" s="11"/>
       <c r="M1" s="11"/>
     </row>
-    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -11737,7 +11737,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -11778,7 +11778,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A4" s="12">
         <f>Emp11Record!B3</f>
         <v>0</v>
@@ -11832,7 +11832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
       <c r="B5" s="14"/>
       <c r="C5" s="12">
@@ -11865,7 +11865,7 @@
       <c r="L5" s="30"/>
       <c r="M5" s="14"/>
     </row>
-    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="C6" s="14"/>
@@ -11892,7 +11892,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -11913,7 +11913,7 @@
       <c r="L7" s="30"/>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -11934,7 +11934,7 @@
       <c r="L8" s="30"/>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -11952,7 +11952,7 @@
       <c r="L9" s="30"/>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -11973,7 +11973,7 @@
       <c r="L10" s="30"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -11991,7 +11991,7 @@
       <c r="L11" s="30"/>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -12009,7 +12009,7 @@
       <c r="L12" s="30"/>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -12027,7 +12027,7 @@
       <c r="L13" s="30"/>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A14" s="15"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -12045,7 +12045,7 @@
       <c r="L14" s="30"/>
       <c r="M14" s="17"/>
     </row>
-    <row r="15" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A15" s="23">
         <f>A4*'Pay Rates'!B3</f>
         <v>0</v>
@@ -12099,7 +12099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
         <v>30</v>
       </c>
@@ -12119,7 +12119,7 @@
       <c r="L16" s="20"/>
       <c r="M16" s="21"/>
     </row>
-    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -12134,7 +12134,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -12149,7 +12149,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
     </row>
-    <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -12166,7 +12166,7 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
     </row>
-    <row r="20" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -12181,7 +12181,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:13" ht="32" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>1</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A22" s="12">
         <f>Emp12Record!B3</f>
         <v>0</v>
@@ -12276,7 +12276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="12">
@@ -12309,7 +12309,7 @@
       <c r="L23" s="30"/>
       <c r="M23" s="14"/>
     </row>
-    <row r="24" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="14"/>
@@ -12336,7 +12336,7 @@
       <c r="L24" s="30"/>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -12357,7 +12357,7 @@
       <c r="L25" s="30"/>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -12378,7 +12378,7 @@
       <c r="L26" s="30"/>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A27" s="15"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -12396,7 +12396,7 @@
       <c r="L27" s="30"/>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -12417,7 +12417,7 @@
       <c r="L28" s="30"/>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A29" s="15"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -12435,7 +12435,7 @@
       <c r="L29" s="30"/>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A30" s="15"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -12453,7 +12453,7 @@
       <c r="L30" s="30"/>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -12471,7 +12471,7 @@
       <c r="L31" s="30"/>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A32" s="15"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -12489,7 +12489,7 @@
       <c r="L32" s="30"/>
       <c r="M32" s="17"/>
     </row>
-    <row r="33" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A33" s="23">
         <f>A22*'Pay Rates'!B3</f>
         <v>0</v>
@@ -12543,7 +12543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
         <v>30</v>
       </c>
@@ -12575,9 +12575,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>25</v>
       </c>
@@ -12594,7 +12594,7 @@
       <c r="L1" s="11"/>
       <c r="M1" s="11"/>
     </row>
-    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -12609,7 +12609,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -12650,7 +12650,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A4" s="12">
         <f>Emp13Record!B3</f>
         <v>0</v>
@@ -12704,7 +12704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
       <c r="B5" s="14"/>
       <c r="C5" s="12">
@@ -12737,7 +12737,7 @@
       <c r="L5" s="30"/>
       <c r="M5" s="14"/>
     </row>
-    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="C6" s="14"/>
@@ -12764,7 +12764,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -12785,7 +12785,7 @@
       <c r="L7" s="30"/>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -12806,7 +12806,7 @@
       <c r="L8" s="30"/>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -12824,7 +12824,7 @@
       <c r="L9" s="30"/>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -12845,7 +12845,7 @@
       <c r="L10" s="30"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -12863,7 +12863,7 @@
       <c r="L11" s="30"/>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -12881,7 +12881,7 @@
       <c r="L12" s="30"/>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -12899,7 +12899,7 @@
       <c r="L13" s="30"/>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A14" s="15"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -12917,7 +12917,7 @@
       <c r="L14" s="30"/>
       <c r="M14" s="17"/>
     </row>
-    <row r="15" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A15" s="23">
         <f>A4*'Pay Rates'!B3</f>
         <v>0</v>
@@ -12971,7 +12971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
         <v>30</v>
       </c>
@@ -12991,7 +12991,7 @@
       <c r="L16" s="20"/>
       <c r="M16" s="21"/>
     </row>
-    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -13006,7 +13006,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -13021,7 +13021,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
     </row>
-    <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -13038,7 +13038,7 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
     </row>
-    <row r="20" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -13053,7 +13053,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:13" ht="32" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>1</v>
       </c>
@@ -13094,7 +13094,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A22" s="12">
         <f>Emp14Record!B3</f>
         <v>0</v>
@@ -13148,7 +13148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="12">
@@ -13181,7 +13181,7 @@
       <c r="L23" s="30"/>
       <c r="M23" s="14"/>
     </row>
-    <row r="24" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="14"/>
@@ -13208,7 +13208,7 @@
       <c r="L24" s="30"/>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -13229,7 +13229,7 @@
       <c r="L25" s="30"/>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -13250,7 +13250,7 @@
       <c r="L26" s="30"/>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A27" s="15"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -13268,7 +13268,7 @@
       <c r="L27" s="30"/>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -13289,7 +13289,7 @@
       <c r="L28" s="30"/>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A29" s="15"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -13307,7 +13307,7 @@
       <c r="L29" s="30"/>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A30" s="15"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -13325,7 +13325,7 @@
       <c r="L30" s="30"/>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -13343,7 +13343,7 @@
       <c r="L31" s="30"/>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A32" s="15"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -13361,7 +13361,7 @@
       <c r="L32" s="30"/>
       <c r="M32" s="17"/>
     </row>
-    <row r="33" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A33" s="23">
         <f>A22*'Pay Rates'!B3</f>
         <v>0</v>
@@ -13415,7 +13415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
         <v>30</v>
       </c>
@@ -13447,9 +13447,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A1" s="11" t="s">
         <v>25</v>
       </c>
@@ -13466,7 +13466,7 @@
       <c r="L1" s="11"/>
       <c r="M1" s="11"/>
     </row>
-    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -13481,7 +13481,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -13522,7 +13522,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A4" s="12">
         <f>Emp15Record!B3</f>
         <v>0</v>
@@ -13576,7 +13576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A5" s="14"/>
       <c r="B5" s="14"/>
       <c r="C5" s="12">
@@ -13609,7 +13609,7 @@
       <c r="L5" s="30"/>
       <c r="M5" s="14"/>
     </row>
-    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="C6" s="14"/>
@@ -13636,7 +13636,7 @@
       <c r="L6" s="30"/>
       <c r="M6" s="15"/>
     </row>
-    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -13657,7 +13657,7 @@
       <c r="L7" s="30"/>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -13678,7 +13678,7 @@
       <c r="L8" s="30"/>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A9" s="15"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -13696,7 +13696,7 @@
       <c r="L9" s="30"/>
       <c r="M9" s="15"/>
     </row>
-    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -13717,7 +13717,7 @@
       <c r="L10" s="30"/>
       <c r="M10" s="15"/>
     </row>
-    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A11" s="15"/>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -13735,7 +13735,7 @@
       <c r="L11" s="30"/>
       <c r="M11" s="15"/>
     </row>
-    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A12" s="15"/>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -13753,7 +13753,7 @@
       <c r="L12" s="30"/>
       <c r="M12" s="15"/>
     </row>
-    <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -13771,7 +13771,7 @@
       <c r="L13" s="30"/>
       <c r="M13" s="15"/>
     </row>
-    <row r="14" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A14" s="15"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -13789,7 +13789,7 @@
       <c r="L14" s="30"/>
       <c r="M14" s="17"/>
     </row>
-    <row r="15" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A15" s="23">
         <f>A4*'Pay Rates'!B3</f>
         <v>0</v>
@@ -13843,7 +13843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
         <v>30</v>
       </c>
@@ -13863,7 +13863,7 @@
       <c r="L16" s="20"/>
       <c r="M16" s="21"/>
     </row>
-    <row r="17" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A17" s="11"/>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>
@@ -13878,7 +13878,7 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A18" s="11"/>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -13893,7 +13893,7 @@
       <c r="L18" s="11"/>
       <c r="M18" s="11"/>
     </row>
-    <row r="19" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -13910,7 +13910,7 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
     </row>
-    <row r="20" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A20" s="11"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -13925,7 +13925,7 @@
       <c r="L20" s="11"/>
       <c r="M20" s="11"/>
     </row>
-    <row r="21" spans="1:13" ht="32" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:13" ht="30" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>1</v>
       </c>
@@ -13966,7 +13966,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A22" s="12"/>
       <c r="B22" s="13"/>
       <c r="C22" s="12"/>
@@ -13981,7 +13981,7 @@
       <c r="L22" s="39"/>
       <c r="M22" s="38"/>
     </row>
-    <row r="23" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A23" s="14"/>
       <c r="B23" s="14"/>
       <c r="C23" s="12"/>
@@ -13996,7 +13996,7 @@
       <c r="L23" s="30"/>
       <c r="M23" s="14"/>
     </row>
-    <row r="24" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="14"/>
@@ -14011,7 +14011,7 @@
       <c r="L24" s="30"/>
       <c r="M24" s="15"/>
     </row>
-    <row r="25" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -14026,7 +14026,7 @@
       <c r="L25" s="30"/>
       <c r="M25" s="15"/>
     </row>
-    <row r="26" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
@@ -14041,7 +14041,7 @@
       <c r="L26" s="30"/>
       <c r="M26" s="15"/>
     </row>
-    <row r="27" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A27" s="15"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15"/>
@@ -14056,7 +14056,7 @@
       <c r="L27" s="30"/>
       <c r="M27" s="15"/>
     </row>
-    <row r="28" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
@@ -14071,7 +14071,7 @@
       <c r="L28" s="30"/>
       <c r="M28" s="15"/>
     </row>
-    <row r="29" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A29" s="15"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
@@ -14086,7 +14086,7 @@
       <c r="L29" s="30"/>
       <c r="M29" s="15"/>
     </row>
-    <row r="30" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A30" s="15"/>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -14101,7 +14101,7 @@
       <c r="L30" s="30"/>
       <c r="M30" s="15"/>
     </row>
-    <row r="31" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A31" s="15"/>
       <c r="B31" s="15"/>
       <c r="C31" s="15"/>
@@ -14116,7 +14116,7 @@
       <c r="L31" s="30"/>
       <c r="M31" s="15"/>
     </row>
-    <row r="32" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A32" s="15"/>
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
@@ -14131,7 +14131,7 @@
       <c r="L32" s="30"/>
       <c r="M32" s="17"/>
     </row>
-    <row r="33" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A33" s="23"/>
       <c r="B33" s="23"/>
       <c r="C33" s="23"/>
@@ -14146,7 +14146,7 @@
       <c r="L33" s="23"/>
       <c r="M33" s="23"/>
     </row>
-    <row r="34" spans="1:13" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:13" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
         <v>30</v>
       </c>
